--- a/on_call_rota_16people_colored.xlsx
+++ b/on_call_rota_16people_colored.xlsx
@@ -29,7 +29,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -54,12 +54,6 @@
         <bgColor rgb="00FFFF99"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF6347"/>
-        <bgColor rgb="00FF6347"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -79,7 +73,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -87,7 +81,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -469,82 +462,82 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Alice</t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Bob</t>
+          <t>Frances</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Charlie</t>
+          <t>MarkHac</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Diana</t>
+          <t>Gavin</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Amy</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Fiona</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>George</t>
+          <t>HannahW</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Hannah</t>
+          <t>Morgan</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>Dowan</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Jane</t>
+          <t>John</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Karl</t>
+          <t>HannahP</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Liam</t>
+          <t>Kirsten</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Mona</t>
+          <t>David</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Nina</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Oliver</t>
+          <t>Gus</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>MarkHol</t>
         </is>
       </c>
     </row>
@@ -559,7 +552,12 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -576,7 +574,12 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -593,7 +596,17 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -615,7 +628,7 @@
           <t>WC SM</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -637,7 +650,7 @@
           <t>WC SM</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -654,7 +667,17 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -671,9 +694,14 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -688,9 +716,14 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -705,7 +738,12 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="R10" s="2" t="inlineStr">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -722,7 +760,17 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -739,14 +787,14 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>WC UHB</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>WC UHB</t>
         </is>
       </c>
     </row>
@@ -761,14 +809,14 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>WC UHB</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>WC UHB</t>
         </is>
       </c>
     </row>
@@ -783,9 +831,24 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -800,9 +863,24 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -817,14 +895,24 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Study Leave</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -839,9 +927,24 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -856,9 +959,29 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -873,12 +996,12 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -895,12 +1018,12 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -917,7 +1040,7 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="R21" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -934,7 +1057,7 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -951,12 +1074,7 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>Sick Leave</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -973,12 +1091,7 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="J24" s="5" t="inlineStr">
-        <is>
-          <t>Sick Leave</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -995,14 +1108,19 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>Sick Leave</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -1017,12 +1135,12 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
       </c>
-      <c r="L26" s="4" t="inlineStr">
+      <c r="Q26" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -1039,12 +1157,12 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
       </c>
-      <c r="L27" s="4" t="inlineStr">
+      <c r="Q27" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -1061,7 +1179,12 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1078,7 +1201,12 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1095,7 +1223,12 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1112,9 +1245,19 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -1129,9 +1272,19 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1299,12 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="N33" s="3" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
       </c>
-      <c r="R33" s="4" t="inlineStr">
+      <c r="I33" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -1168,12 +1321,12 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="N34" s="3" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
       </c>
-      <c r="R34" s="4" t="inlineStr">
+      <c r="I34" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -1190,9 +1343,24 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1375,17 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>Annual Leave</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1229,14 +1402,19 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>Annual Leave</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -1251,14 +1429,24 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>Annual Leave</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -1273,14 +1461,34 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>Annual Leave</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1503,12 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="M40" s="3" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
       </c>
-      <c r="P40" s="4" t="inlineStr">
+      <c r="J40" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -1317,12 +1525,12 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="M41" s="3" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
       </c>
-      <c r="P41" s="4" t="inlineStr">
+      <c r="J41" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -1339,9 +1547,24 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1579,22 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="O43" s="2" t="inlineStr">
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1373,9 +1611,19 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1638,17 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1407,14 +1665,19 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
-      <c r="M46" s="5" t="inlineStr">
-        <is>
-          <t>Annual Leave</t>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -1429,14 +1692,14 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>WC UHB</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
-        </is>
-      </c>
-      <c r="Q47" s="4" t="inlineStr">
-        <is>
-          <t>WC UHB</t>
         </is>
       </c>
     </row>
@@ -1451,14 +1714,14 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>WC UHB</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
-        </is>
-      </c>
-      <c r="Q48" s="4" t="inlineStr">
-        <is>
-          <t>WC UHB</t>
         </is>
       </c>
     </row>
@@ -1473,9 +1736,19 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -1490,9 +1763,19 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="P50" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -1507,9 +1790,19 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1817,17 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr">
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1541,7 +1844,17 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1558,12 +1871,12 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
+      <c r="G54" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
       </c>
-      <c r="I54" s="4" t="inlineStr">
+      <c r="K54" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -1580,12 +1893,12 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr">
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
       </c>
-      <c r="I55" s="4" t="inlineStr">
+      <c r="K55" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -1602,7 +1915,22 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1619,7 +1947,17 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="R57" s="2" t="inlineStr">
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1636,7 +1974,17 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="Q58" s="2" t="inlineStr">
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1653,9 +2001,24 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="O59" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -1670,12 +2033,12 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>BH SM</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>BH UHB</t>
         </is>
@@ -1692,12 +2055,12 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="L61" s="4" t="inlineStr">
+      <c r="I61" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
       </c>
-      <c r="M61" s="3" t="inlineStr">
+      <c r="P61" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
@@ -1714,12 +2077,12 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="L62" s="4" t="inlineStr">
+      <c r="I62" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
       </c>
-      <c r="M62" s="3" t="inlineStr">
+      <c r="P62" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
@@ -1736,7 +2099,7 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>BH SM</t>
         </is>
@@ -1758,9 +2121,24 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -1775,14 +2153,24 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
-      <c r="L65" s="5" t="inlineStr">
-        <is>
-          <t>Conference</t>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -1797,9 +2185,24 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -1814,9 +2217,34 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="O67" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -1831,7 +2259,7 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="G68" s="3" t="inlineStr">
+      <c r="N68" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
@@ -1853,7 +2281,7 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="G69" s="3" t="inlineStr">
+      <c r="N69" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
@@ -1875,7 +2303,42 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="L70" s="2" t="inlineStr">
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1892,9 +2355,44 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="M71" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -1909,7 +2407,42 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="J72" s="2" t="inlineStr">
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1926,9 +2459,49 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -1943,9 +2516,49 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -1960,14 +2573,14 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="F75" s="3" t="inlineStr">
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>WC UHB</t>
+        </is>
+      </c>
+      <c r="R75" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
-        </is>
-      </c>
-      <c r="I75" s="4" t="inlineStr">
-        <is>
-          <t>WC UHB</t>
         </is>
       </c>
     </row>
@@ -1982,14 +2595,14 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="F76" s="3" t="inlineStr">
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t>WC UHB</t>
+        </is>
+      </c>
+      <c r="R76" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
-        </is>
-      </c>
-      <c r="I76" s="4" t="inlineStr">
-        <is>
-          <t>WC UHB</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2617,37 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -2021,9 +2664,39 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -2038,14 +2711,29 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D79" s="5" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="P79" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -2060,9 +2748,29 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="N80" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2785,32 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -2094,12 +2827,12 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="E82" s="3" t="inlineStr">
+      <c r="H82" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
       </c>
-      <c r="K82" s="4" t="inlineStr">
+      <c r="L82" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -2116,12 +2849,12 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="E83" s="3" t="inlineStr">
+      <c r="H83" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
       </c>
-      <c r="K83" s="4" t="inlineStr">
+      <c r="L83" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -2138,9 +2871,29 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -2155,9 +2908,19 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -2172,9 +2935,19 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="O86" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2962,12 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -2206,14 +2984,29 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="I88" s="5" t="inlineStr">
-        <is>
-          <t>Annual Leave</t>
-        </is>
-      </c>
-      <c r="P88" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -2228,12 +3021,12 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D89" s="3" t="inlineStr">
+      <c r="F89" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
       </c>
-      <c r="R89" s="4" t="inlineStr">
+      <c r="M89" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -2250,12 +3043,12 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D90" s="3" t="inlineStr">
+      <c r="F90" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
       </c>
-      <c r="R90" s="4" t="inlineStr">
+      <c r="M90" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -2272,14 +3065,14 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>BH UHB</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
         <is>
           <t>BH SM</t>
-        </is>
-      </c>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>BH UHB</t>
         </is>
       </c>
     </row>
@@ -2294,7 +3087,12 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -2311,7 +3109,12 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="K93" s="2" t="inlineStr">
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -2328,7 +3131,12 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="M94" s="2" t="inlineStr">
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -2345,9 +3153,14 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -2367,7 +3180,7 @@
           <t>WC SM</t>
         </is>
       </c>
-      <c r="O96" s="4" t="inlineStr">
+      <c r="I96" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -2389,7 +3202,7 @@
           <t>WC SM</t>
         </is>
       </c>
-      <c r="O97" s="4" t="inlineStr">
+      <c r="I97" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -2406,14 +3219,19 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="P98" s="5" t="inlineStr">
-        <is>
-          <t>Sick Leave</t>
-        </is>
-      </c>
-      <c r="R98" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -2428,14 +3246,14 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
-      <c r="P99" s="5" t="inlineStr">
-        <is>
-          <t>Sick Leave</t>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -2450,9 +3268,14 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="Q100" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -2467,7 +3290,12 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -2484,14 +3312,14 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="C102" s="5" t="inlineStr">
-        <is>
-          <t>Conference</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -2506,14 +3334,14 @@
           <t>Saturday</t>
         </is>
       </c>
+      <c r="I103" s="4" t="inlineStr">
+        <is>
+          <t>WC UHB</t>
+        </is>
+      </c>
       <c r="N103" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
-        </is>
-      </c>
-      <c r="P103" s="4" t="inlineStr">
-        <is>
-          <t>WC UHB</t>
         </is>
       </c>
     </row>
@@ -2528,14 +3356,14 @@
           <t>Sunday</t>
         </is>
       </c>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t>WC UHB</t>
+        </is>
+      </c>
       <c r="N104" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
-        </is>
-      </c>
-      <c r="P104" s="4" t="inlineStr">
-        <is>
-          <t>WC UHB</t>
         </is>
       </c>
     </row>
@@ -2550,9 +3378,14 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -2567,7 +3400,12 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -2584,9 +3422,14 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -2601,9 +3444,19 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -2618,9 +3471,29 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="J109" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="P109" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -2635,12 +3508,12 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="H110" s="3" t="inlineStr">
+      <c r="E110" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
       </c>
-      <c r="L110" s="4" t="inlineStr">
+      <c r="K110" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -2657,12 +3530,12 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="H111" s="3" t="inlineStr">
+      <c r="E111" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
       </c>
-      <c r="L111" s="4" t="inlineStr">
+      <c r="K111" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -2679,12 +3552,12 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="F112" t="inlineStr">
         <is>
           <t>BH SM</t>
         </is>
       </c>
-      <c r="P112" t="inlineStr">
+      <c r="I112" t="inlineStr">
         <is>
           <t>BH UHB</t>
         </is>
@@ -2701,9 +3574,39 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="N113" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -2718,9 +3621,39 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="P114" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -2735,9 +3668,39 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="K115" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -2752,9 +3715,44 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="N116" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -2769,12 +3767,12 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="M117" s="3" t="inlineStr">
+      <c r="F117" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
       </c>
-      <c r="O117" s="4" t="inlineStr">
+      <c r="L117" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -2791,12 +3789,12 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="M118" s="3" t="inlineStr">
+      <c r="F118" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
       </c>
-      <c r="O118" s="4" t="inlineStr">
+      <c r="L118" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -2813,9 +3811,29 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="R119" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>OffRota</t>
         </is>
       </c>
     </row>
@@ -2830,9 +3848,29 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="L120" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>OffRota</t>
         </is>
       </c>
     </row>
@@ -2847,14 +3885,29 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="F121" s="5" t="inlineStr">
-        <is>
-          <t>Annual Leave</t>
-        </is>
-      </c>
-      <c r="Q121" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>OffRota</t>
         </is>
       </c>
     </row>
@@ -2869,14 +3922,29 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="F122" s="5" t="inlineStr">
-        <is>
-          <t>Annual Leave</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="P122" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>OffRota</t>
         </is>
       </c>
     </row>
@@ -2891,12 +3959,22 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="F123" s="5" t="inlineStr">
-        <is>
-          <t>Annual Leave</t>
-        </is>
-      </c>
-      <c r="L123" s="2" t="inlineStr">
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>OffRota</t>
+        </is>
+      </c>
+      <c r="R123" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -2913,14 +3991,14 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="G124" s="3" t="inlineStr">
+      <c r="K124" s="4" t="inlineStr">
+        <is>
+          <t>WC UHB</t>
+        </is>
+      </c>
+      <c r="O124" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
-        </is>
-      </c>
-      <c r="K124" s="4" t="inlineStr">
-        <is>
-          <t>WC UHB</t>
         </is>
       </c>
     </row>
@@ -2935,14 +4013,14 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="G125" s="3" t="inlineStr">
+      <c r="K125" s="4" t="inlineStr">
+        <is>
+          <t>WC UHB</t>
+        </is>
+      </c>
+      <c r="O125" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
-        </is>
-      </c>
-      <c r="K125" s="4" t="inlineStr">
-        <is>
-          <t>WC UHB</t>
         </is>
       </c>
     </row>
@@ -2957,9 +4035,24 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="M126" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>OffRota</t>
         </is>
       </c>
     </row>
@@ -2974,9 +4067,19 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="O127" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>OffRota</t>
         </is>
       </c>
     </row>
@@ -2991,14 +4094,19 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="J128" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
-      <c r="K128" s="5" t="inlineStr">
-        <is>
-          <t>Training</t>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>OffRota</t>
+        </is>
+      </c>
+      <c r="R128" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -3013,9 +4121,19 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D129" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>OffRota</t>
         </is>
       </c>
     </row>
@@ -3030,9 +4148,24 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="R130" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>OffRota</t>
         </is>
       </c>
     </row>
@@ -3047,14 +4180,14 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="F131" s="3" t="inlineStr">
+      <c r="I131" s="4" t="inlineStr">
+        <is>
+          <t>WC UHB</t>
+        </is>
+      </c>
+      <c r="P131" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
-        </is>
-      </c>
-      <c r="I131" s="4" t="inlineStr">
-        <is>
-          <t>WC UHB</t>
         </is>
       </c>
     </row>
@@ -3069,14 +4202,14 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="F132" s="3" t="inlineStr">
+      <c r="I132" s="4" t="inlineStr">
+        <is>
+          <t>WC UHB</t>
+        </is>
+      </c>
+      <c r="P132" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
-        </is>
-      </c>
-      <c r="I132" s="4" t="inlineStr">
-        <is>
-          <t>WC UHB</t>
         </is>
       </c>
     </row>
@@ -3091,9 +4224,19 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>OffRota</t>
         </is>
       </c>
     </row>
@@ -3108,7 +4251,17 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="K134" s="2" t="inlineStr">
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>OffRota</t>
+        </is>
+      </c>
+      <c r="R134" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -3125,9 +4278,19 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="L135" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>OffRota</t>
         </is>
       </c>
     </row>
@@ -3142,9 +4305,24 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="M136" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>OffRota</t>
         </is>
       </c>
     </row>
@@ -3159,9 +4337,34 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="K137" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>OffRota</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -3176,12 +4379,12 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C138" s="3" t="inlineStr">
+      <c r="G138" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
       </c>
-      <c r="R138" s="4" t="inlineStr">
+      <c r="L138" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -3198,12 +4401,12 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C139" s="3" t="inlineStr">
+      <c r="G139" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
       </c>
-      <c r="R139" s="4" t="inlineStr">
+      <c r="L139" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -3220,9 +4423,24 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>OffRota</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -3242,6 +4460,16 @@
           <t>On Call</t>
         </is>
       </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>OffRota</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3254,9 +4482,19 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="O142" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>OffRota</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -3271,9 +4509,19 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>OffRota</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -3288,9 +4536,24 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="O144" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>OffRota</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>UA</t>
         </is>
       </c>
     </row>
@@ -3305,12 +4568,12 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="E145" s="3" t="inlineStr">
+      <c r="H145" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
       </c>
-      <c r="Q145" s="4" t="inlineStr">
+      <c r="J145" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -3327,12 +4590,12 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="E146" s="3" t="inlineStr">
+      <c r="H146" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
       </c>
-      <c r="Q146" s="4" t="inlineStr">
+      <c r="J146" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -3349,9 +4612,19 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="R147" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>OffRota</t>
         </is>
       </c>
     </row>
@@ -3366,9 +4639,24 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>OffRota</t>
         </is>
       </c>
     </row>
@@ -3383,14 +4671,24 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="E149" s="5" t="inlineStr">
-        <is>
-          <t>Annual Leave</t>
-        </is>
-      </c>
-      <c r="F149" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>OffRota</t>
         </is>
       </c>
     </row>
@@ -3405,14 +4703,24 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="E150" s="5" t="inlineStr">
-        <is>
-          <t>Annual Leave</t>
-        </is>
-      </c>
-      <c r="P150" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>OffRota</t>
         </is>
       </c>
     </row>
@@ -3427,14 +4735,29 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="E151" s="5" t="inlineStr">
-        <is>
-          <t>Annual Leave</t>
-        </is>
-      </c>
-      <c r="G151" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>OffRota</t>
         </is>
       </c>
     </row>
@@ -3449,14 +4772,14 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D152" s="3" t="inlineStr">
+      <c r="J152" s="4" t="inlineStr">
+        <is>
+          <t>WC UHB</t>
+        </is>
+      </c>
+      <c r="R152" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
-        </is>
-      </c>
-      <c r="J152" s="4" t="inlineStr">
-        <is>
-          <t>WC UHB</t>
         </is>
       </c>
     </row>
@@ -3471,14 +4794,14 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D153" s="3" t="inlineStr">
+      <c r="J153" s="4" t="inlineStr">
+        <is>
+          <t>WC UHB</t>
+        </is>
+      </c>
+      <c r="R153" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
-        </is>
-      </c>
-      <c r="J153" s="4" t="inlineStr">
-        <is>
-          <t>WC UHB</t>
         </is>
       </c>
     </row>
@@ -3493,9 +4816,19 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="Q154" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>OffRota</t>
         </is>
       </c>
     </row>
@@ -3510,9 +4843,24 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>OffRota</t>
         </is>
       </c>
     </row>
@@ -3527,9 +4875,19 @@
           <t>Wednesday</t>
         </is>
       </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>OffRota</t>
         </is>
       </c>
     </row>
@@ -3544,9 +4902,19 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="K157" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="P157" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>OffRota</t>
         </is>
       </c>
     </row>
@@ -3561,9 +4929,24 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="Q158" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>OffRota</t>
         </is>
       </c>
     </row>
@@ -3578,12 +4961,12 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="N159" s="3" t="inlineStr">
+      <c r="C159" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
       </c>
-      <c r="P159" s="4" t="inlineStr">
+      <c r="J159" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -3600,12 +4983,12 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="N160" s="3" t="inlineStr">
+      <c r="C160" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
       </c>
-      <c r="P160" s="4" t="inlineStr">
+      <c r="J160" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -3622,9 +5005,19 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="L161" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>OffRota</t>
         </is>
       </c>
     </row>
@@ -3639,6 +5032,21 @@
           <t>Tuesday</t>
         </is>
       </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>OffRota</t>
+        </is>
+      </c>
       <c r="R162" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
@@ -3656,9 +5064,24 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="O163" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>OffRota</t>
         </is>
       </c>
     </row>
@@ -3673,9 +5096,24 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>OffRota</t>
         </is>
       </c>
     </row>
@@ -3690,9 +5128,24 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="M165" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>OffRota</t>
         </is>
       </c>
     </row>
@@ -3707,14 +5160,14 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="F166" s="3" t="inlineStr">
+      <c r="M166" s="4" t="inlineStr">
+        <is>
+          <t>WC UHB</t>
+        </is>
+      </c>
+      <c r="N166" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
-        </is>
-      </c>
-      <c r="Q166" s="4" t="inlineStr">
-        <is>
-          <t>WC UHB</t>
         </is>
       </c>
     </row>
@@ -3729,14 +5182,14 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="F167" s="3" t="inlineStr">
+      <c r="M167" s="4" t="inlineStr">
+        <is>
+          <t>WC UHB</t>
+        </is>
+      </c>
+      <c r="N167" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
-        </is>
-      </c>
-      <c r="Q167" s="4" t="inlineStr">
-        <is>
-          <t>WC UHB</t>
         </is>
       </c>
     </row>
@@ -3751,9 +5204,29 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="N168" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>OffRota</t>
         </is>
       </c>
     </row>
@@ -3768,7 +5241,22 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="M169" s="2" t="inlineStr">
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>OffRota</t>
+        </is>
+      </c>
+      <c r="R169" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -3785,9 +5273,19 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D170" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>OffRota</t>
         </is>
       </c>
     </row>
@@ -3807,6 +5305,16 @@
           <t>On Call</t>
         </is>
       </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>OffRota</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -3819,9 +5327,14 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>OffRota</t>
         </is>
       </c>
     </row>
@@ -3836,12 +5349,12 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="G173" s="3" t="inlineStr">
+      <c r="D173" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
       </c>
-      <c r="I173" s="4" t="inlineStr">
+      <c r="K173" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -3858,12 +5371,12 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="G174" s="3" t="inlineStr">
+      <c r="D174" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
       </c>
-      <c r="I174" s="4" t="inlineStr">
+      <c r="K174" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -3880,9 +5393,19 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="Q175" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>OffRota</t>
         </is>
       </c>
     </row>
@@ -3897,9 +5420,19 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>OffRota</t>
         </is>
       </c>
     </row>
@@ -3914,9 +5447,19 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>OffRota</t>
         </is>
       </c>
     </row>
@@ -3936,6 +5479,16 @@
           <t>On Call</t>
         </is>
       </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>OffRota</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -3948,9 +5501,24 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="P179" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>OffRota</t>
         </is>
       </c>
     </row>
@@ -3965,14 +5533,14 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="M180" s="3" t="inlineStr">
+      <c r="J180" s="4" t="inlineStr">
+        <is>
+          <t>WC UHB</t>
+        </is>
+      </c>
+      <c r="O180" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
-        </is>
-      </c>
-      <c r="O180" s="4" t="inlineStr">
-        <is>
-          <t>WC UHB</t>
         </is>
       </c>
     </row>
@@ -3987,14 +5555,14 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="M181" s="3" t="inlineStr">
+      <c r="J181" s="4" t="inlineStr">
+        <is>
+          <t>WC UHB</t>
+        </is>
+      </c>
+      <c r="O181" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
-        </is>
-      </c>
-      <c r="O181" s="4" t="inlineStr">
-        <is>
-          <t>WC UHB</t>
         </is>
       </c>
     </row>
@@ -4009,9 +5577,19 @@
           <t>Monday</t>
         </is>
       </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
       <c r="N182" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>OffRota</t>
         </is>
       </c>
     </row>
@@ -4026,9 +5604,19 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="P183" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="L183" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>OffRota</t>
         </is>
       </c>
     </row>
@@ -4043,9 +5631,19 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="J184" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="K184" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>OffRota</t>
         </is>
       </c>
     </row>

--- a/on_call_rota_16people_colored.xlsx
+++ b/on_call_rota_16people_colored.xlsx
@@ -557,7 +557,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -667,6 +667,11 @@
           <t>Monday</t>
         </is>
       </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>UA</t>
@@ -675,11 +680,6 @@
       <c r="N7" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -716,14 +716,14 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -760,6 +760,11 @@
           <t>Friday</t>
         </is>
       </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>UA</t>
@@ -768,11 +773,6 @@
       <c r="H11" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
           <t>Academic</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -996,12 +996,12 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="Q19" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -1018,12 +1018,12 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="Q20" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -1091,7 +1091,7 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1108,11 +1108,6 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>UA</t>
@@ -1121,6 +1116,11 @@
       <c r="M25" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -1135,14 +1135,14 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>WC UHB</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
-        </is>
-      </c>
-      <c r="Q26" s="4" t="inlineStr">
-        <is>
-          <t>WC UHB</t>
         </is>
       </c>
     </row>
@@ -1157,14 +1157,14 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>WC UHB</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
-        </is>
-      </c>
-      <c r="Q27" s="4" t="inlineStr">
-        <is>
-          <t>WC UHB</t>
         </is>
       </c>
     </row>
@@ -1179,14 +1179,14 @@
           <t>Monday</t>
         </is>
       </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="R29" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1228,7 +1228,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1245,14 +1245,14 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -1272,7 +1272,7 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1299,7 +1299,7 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
@@ -1321,7 +1321,7 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
@@ -1429,7 +1429,7 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1471,14 +1471,14 @@
           <t>UA</t>
         </is>
       </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -1503,14 +1503,14 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>WC UHB</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
-        </is>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>WC UHB</t>
         </is>
       </c>
     </row>
@@ -1525,14 +1525,14 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>WC UHB</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
-        </is>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>WC UHB</t>
         </is>
       </c>
     </row>
@@ -1547,14 +1547,14 @@
           <t>Monday</t>
         </is>
       </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -1594,7 +1594,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
+      <c r="R43" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1611,11 +1611,6 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="F44" t="inlineStr">
         <is>
           <t>UA</t>
@@ -1624,6 +1619,11 @@
       <c r="J44" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -1638,6 +1638,11 @@
           <t>Thursday</t>
         </is>
       </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr">
         <is>
           <t>UA</t>
@@ -1646,11 +1651,6 @@
       <c r="J45" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -1670,14 +1670,14 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="J46" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -1692,14 +1692,14 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="L47" s="4" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>WC SM</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
-        </is>
-      </c>
-      <c r="O47" s="3" t="inlineStr">
-        <is>
-          <t>WC SM</t>
         </is>
       </c>
     </row>
@@ -1714,14 +1714,14 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="L48" s="4" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>WC SM</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
-        </is>
-      </c>
-      <c r="O48" s="3" t="inlineStr">
-        <is>
-          <t>WC SM</t>
         </is>
       </c>
     </row>
@@ -1741,14 +1741,14 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="J49" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -1763,11 +1763,6 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="F50" t="inlineStr">
         <is>
           <t>UA</t>
@@ -1776,6 +1771,11 @@
       <c r="J50" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -1795,14 +1795,14 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="J51" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="R52" s="2" t="inlineStr">
+      <c r="N52" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1854,7 +1854,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="O53" s="2" t="inlineStr">
+      <c r="M53" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1871,7 +1871,7 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="G54" s="3" t="inlineStr">
+      <c r="H54" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
@@ -1893,7 +1893,7 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="G55" s="3" t="inlineStr">
+      <c r="H55" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
@@ -1925,14 +1925,14 @@
           <t>UA</t>
         </is>
       </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -1952,14 +1952,14 @@
           <t>UA</t>
         </is>
       </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1984,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="O58" s="2" t="inlineStr">
+      <c r="M58" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -2001,6 +2001,11 @@
           <t>Thursday</t>
         </is>
       </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr">
         <is>
           <t>UA</t>
@@ -2009,11 +2014,6 @@
       <c r="J59" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -2033,7 +2033,7 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>BH SM</t>
         </is>
@@ -2055,12 +2055,12 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="I61" s="4" t="inlineStr">
+      <c r="L61" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
       </c>
-      <c r="P61" s="3" t="inlineStr">
+      <c r="N61" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
@@ -2077,12 +2077,12 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="I62" s="4" t="inlineStr">
+      <c r="L62" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
       </c>
-      <c r="P62" s="3" t="inlineStr">
+      <c r="N62" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
@@ -2099,12 +2099,12 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>BH SM</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>BH UHB</t>
         </is>
@@ -2126,7 +2126,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -2153,11 +2153,6 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="F65" t="inlineStr">
         <is>
           <t>UA</t>
@@ -2171,6 +2166,11 @@
       <c r="M65" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2232,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="K67" s="2" t="inlineStr">
+      <c r="L67" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -2259,7 +2259,7 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="N68" s="3" t="inlineStr">
+      <c r="G68" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
@@ -2281,7 +2281,7 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="N69" s="3" t="inlineStr">
+      <c r="G69" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
@@ -2536,7 +2536,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="L74" s="2" t="inlineStr">
+      <c r="K74" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -2573,7 +2573,7 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="K75" s="4" t="inlineStr">
+      <c r="L75" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -2595,7 +2595,7 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="K76" s="4" t="inlineStr">
+      <c r="L76" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -2617,6 +2617,11 @@
           <t>Monday</t>
         </is>
       </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="F77" t="inlineStr">
         <is>
           <t>UA</t>
@@ -2645,11 +2650,6 @@
       <c r="N77" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="O77" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -2664,11 +2664,6 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="F78" t="inlineStr">
         <is>
           <t>UA</t>
@@ -2697,6 +2692,11 @@
       <c r="N78" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -2748,11 +2748,6 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="F80" t="inlineStr">
         <is>
           <t>UA</t>
@@ -2771,6 +2766,11 @@
       <c r="M80" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -2827,14 +2827,14 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="H82" s="3" t="inlineStr">
+      <c r="K82" s="4" t="inlineStr">
+        <is>
+          <t>WC UHB</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
-        </is>
-      </c>
-      <c r="L82" s="4" t="inlineStr">
-        <is>
-          <t>WC UHB</t>
         </is>
       </c>
     </row>
@@ -2849,14 +2849,14 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="H83" s="3" t="inlineStr">
+      <c r="K83" s="4" t="inlineStr">
+        <is>
+          <t>WC UHB</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
-        </is>
-      </c>
-      <c r="L83" s="4" t="inlineStr">
-        <is>
-          <t>WC UHB</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="K86" s="2" t="inlineStr">
+      <c r="L86" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -2989,11 +2989,6 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="I88" t="inlineStr">
         <is>
           <t>UA</t>
@@ -3002,6 +2997,11 @@
       <c r="J88" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -3065,14 +3065,14 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>BH SM</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
         <is>
           <t>BH UHB</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>BH SM</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3092,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="L92" s="2" t="inlineStr">
+      <c r="K92" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -3175,7 +3175,7 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C96" s="3" t="inlineStr">
+      <c r="H96" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
@@ -3197,7 +3197,7 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C97" s="3" t="inlineStr">
+      <c r="H97" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
@@ -3312,7 +3312,7 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="I102" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -3334,14 +3334,14 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="I103" s="4" t="inlineStr">
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>WC SM</t>
+        </is>
+      </c>
+      <c r="K103" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
-        </is>
-      </c>
-      <c r="N103" s="3" t="inlineStr">
-        <is>
-          <t>WC SM</t>
         </is>
       </c>
     </row>
@@ -3356,14 +3356,14 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="I104" s="4" t="inlineStr">
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>WC SM</t>
+        </is>
+      </c>
+      <c r="K104" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
-        </is>
-      </c>
-      <c r="N104" s="3" t="inlineStr">
-        <is>
-          <t>WC SM</t>
         </is>
       </c>
     </row>
@@ -3400,14 +3400,14 @@
           <t>Tuesday</t>
         </is>
       </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="J106" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="O106" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -3422,7 +3422,7 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="I107" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -3486,7 +3486,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="P109" s="2" t="inlineStr">
+      <c r="K109" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -3513,7 +3513,7 @@
           <t>WC SM</t>
         </is>
       </c>
-      <c r="K110" s="4" t="inlineStr">
+      <c r="L110" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -3535,7 +3535,7 @@
           <t>WC SM</t>
         </is>
       </c>
-      <c r="K111" s="4" t="inlineStr">
+      <c r="L111" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -3636,7 +3636,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="N114" s="2" t="inlineStr">
+      <c r="K114" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -3720,6 +3720,11 @@
           <t>UA</t>
         </is>
       </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="G116" t="inlineStr">
         <is>
           <t>UA</t>
@@ -3733,11 +3738,6 @@
       <c r="J116" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="K116" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -3772,7 +3772,7 @@
           <t>WC SM</t>
         </is>
       </c>
-      <c r="L117" s="4" t="inlineStr">
+      <c r="Q117" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -3794,7 +3794,7 @@
           <t>WC SM</t>
         </is>
       </c>
-      <c r="L118" s="4" t="inlineStr">
+      <c r="Q118" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -3826,14 +3826,14 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="O119" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="Q119" t="inlineStr">
         <is>
           <t>OffRota</t>
+        </is>
+      </c>
+      <c r="R119" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -3848,11 +3848,6 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="I120" t="inlineStr">
         <is>
           <t>UA</t>
@@ -3861,6 +3856,11 @@
       <c r="J120" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -3885,7 +3885,7 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="C121" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -3922,6 +3922,11 @@
           <t>Thursday</t>
         </is>
       </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="I122" t="inlineStr">
         <is>
           <t>UA</t>
@@ -3935,11 +3940,6 @@
       <c r="N122" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="P122" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
@@ -3959,6 +3959,11 @@
           <t>Friday</t>
         </is>
       </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="I123" t="inlineStr">
         <is>
           <t>UA</t>
@@ -3972,11 +3977,6 @@
       <c r="Q123" t="inlineStr">
         <is>
           <t>OffRota</t>
-        </is>
-      </c>
-      <c r="R123" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -3991,7 +3991,7 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="K124" s="4" t="inlineStr">
+      <c r="L124" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -4013,7 +4013,7 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="K125" s="4" t="inlineStr">
+      <c r="L125" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -4035,6 +4035,11 @@
           <t>Monday</t>
         </is>
       </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="I126" t="inlineStr">
         <is>
           <t>UA</t>
@@ -4043,11 +4048,6 @@
       <c r="J126" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="L126" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
@@ -4094,6 +4094,11 @@
           <t>Wednesday</t>
         </is>
       </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="J128" t="inlineStr">
         <is>
           <t>UA</t>
@@ -4102,11 +4107,6 @@
       <c r="Q128" t="inlineStr">
         <is>
           <t>OffRota</t>
-        </is>
-      </c>
-      <c r="R128" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -4121,14 +4121,14 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="J129" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
@@ -4153,11 +4153,6 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="J130" t="inlineStr">
         <is>
           <t>UA</t>
@@ -4166,6 +4161,11 @@
       <c r="Q130" t="inlineStr">
         <is>
           <t>OffRota</t>
+        </is>
+      </c>
+      <c r="R130" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -4229,7 +4229,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="K133" s="2" t="inlineStr">
+      <c r="L133" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -4256,14 +4256,14 @@
           <t>UA</t>
         </is>
       </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="Q134" t="inlineStr">
         <is>
           <t>OffRota</t>
-        </is>
-      </c>
-      <c r="R134" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -4278,11 +4278,6 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="J135" t="inlineStr">
         <is>
           <t>UA</t>
@@ -4291,6 +4286,11 @@
       <c r="Q135" t="inlineStr">
         <is>
           <t>OffRota</t>
+        </is>
+      </c>
+      <c r="R135" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4305,7 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -4337,14 +4337,14 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="D137" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -4384,7 +4384,7 @@
           <t>WC SM</t>
         </is>
       </c>
-      <c r="L138" s="4" t="inlineStr">
+      <c r="K138" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -4406,7 +4406,7 @@
           <t>WC SM</t>
         </is>
       </c>
-      <c r="L139" s="4" t="inlineStr">
+      <c r="K139" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -4455,7 +4455,7 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="I141" s="2" t="inlineStr">
+      <c r="L141" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -4482,7 +4482,7 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="K142" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -4509,7 +4509,7 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="N143" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -4541,7 +4541,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="L144" s="2" t="inlineStr">
+      <c r="I144" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -4568,7 +4568,7 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="H145" s="3" t="inlineStr">
+      <c r="C145" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
@@ -4590,7 +4590,7 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="H146" s="3" t="inlineStr">
+      <c r="C146" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
@@ -4617,7 +4617,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="K147" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -4644,7 +4644,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -4676,14 +4676,14 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="L149" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="O149" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="P149" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="Q149" t="inlineStr">
@@ -4745,7 +4745,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="I151" s="2" t="inlineStr">
+      <c r="L151" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -4772,7 +4772,7 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="J152" s="4" t="inlineStr">
+      <c r="I152" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -4794,7 +4794,7 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="J153" s="4" t="inlineStr">
+      <c r="I153" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -4821,7 +4821,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr">
+      <c r="J154" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -4880,7 +4880,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="I156" s="2" t="inlineStr">
+      <c r="K156" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -4907,7 +4907,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="P157" s="2" t="inlineStr">
+      <c r="L157" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -4961,7 +4961,7 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C159" s="3" t="inlineStr">
+      <c r="H159" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
@@ -4983,7 +4983,7 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C160" s="3" t="inlineStr">
+      <c r="H160" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
@@ -5074,7 +5074,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="L163" s="2" t="inlineStr">
+      <c r="O163" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -5101,14 +5101,14 @@
           <t>UA</t>
         </is>
       </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="I164" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="K164" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">
@@ -5128,6 +5128,11 @@
           <t>Friday</t>
         </is>
       </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="D165" t="inlineStr">
         <is>
           <t>UA</t>
@@ -5136,11 +5141,6 @@
       <c r="I165" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="J165" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
       <c r="Q165" t="inlineStr">
@@ -5214,14 +5214,14 @@
           <t>UA</t>
         </is>
       </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="N168" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="O168" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
       <c r="Q168" t="inlineStr">
@@ -5273,14 +5273,14 @@
           <t>Wednesday</t>
         </is>
       </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="I170" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="J170" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
       <c r="Q170" t="inlineStr">
@@ -5300,14 +5300,14 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="I171" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="Q171" t="inlineStr">
@@ -5354,7 +5354,7 @@
           <t>WC SM</t>
         </is>
       </c>
-      <c r="K173" s="4" t="inlineStr">
+      <c r="J173" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -5376,7 +5376,7 @@
           <t>WC SM</t>
         </is>
       </c>
-      <c r="K174" s="4" t="inlineStr">
+      <c r="J174" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -5393,7 +5393,7 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="J175" s="2" t="inlineStr">
+      <c r="I175" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -5420,7 +5420,7 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="I176" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -5447,14 +5447,14 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="N177" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="P177" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="Q177" t="inlineStr">
@@ -5511,7 +5511,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="P179" s="2" t="inlineStr">
+      <c r="J179" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -5533,7 +5533,7 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="J180" s="4" t="inlineStr">
+      <c r="L180" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -5555,7 +5555,7 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="J181" s="4" t="inlineStr">
+      <c r="L181" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -5604,14 +5604,14 @@
           <t>Tuesday</t>
         </is>
       </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="I183" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="L183" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
       <c r="Q183" t="inlineStr">
@@ -5636,7 +5636,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="K184" s="2" t="inlineStr">
+      <c r="J184" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>

--- a/on_call_rota_16people_colored.xlsx
+++ b/on_call_rota_16people_colored.xlsx
@@ -596,6 +596,11 @@
           <t>Friday</t>
         </is>
       </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>UA</t>
@@ -604,11 +609,6 @@
       <c r="P4" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -738,14 +738,14 @@
           <t>Thursday</t>
         </is>
       </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -760,11 +760,6 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>UA</t>
@@ -773,6 +768,11 @@
       <c r="H11" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -836,11 +836,6 @@
           <t>Academic</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr">
         <is>
           <t>UA</t>
@@ -849,6 +844,11 @@
       <c r="O14" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -863,14 +863,14 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Academic</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -895,14 +895,14 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Academic</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -932,7 +932,7 @@
           <t>Academic</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -964,7 +964,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1040,7 +1040,7 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="R21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1057,7 +1057,7 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1074,7 +1074,7 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1091,7 +1091,7 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1118,7 +1118,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1179,7 +1179,7 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1201,14 +1201,14 @@
           <t>Tuesday</t>
         </is>
       </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -1223,14 +1223,14 @@
           <t>Wednesday</t>
         </is>
       </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -1250,14 +1250,14 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -1272,14 +1272,14 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -1343,6 +1343,11 @@
           <t>Monday</t>
         </is>
       </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>UA</t>
@@ -1351,11 +1356,6 @@
       <c r="M35" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -1380,14 +1380,14 @@
           <t>UA</t>
         </is>
       </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="O36" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -1402,14 +1402,14 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -1429,7 +1429,7 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1547,11 +1547,6 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="F42" t="inlineStr">
         <is>
           <t>UA</t>
@@ -1565,6 +1560,11 @@
       <c r="J42" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -1584,6 +1584,11 @@
           <t>UA</t>
         </is>
       </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>UA</t>
@@ -1592,11 +1597,6 @@
       <c r="J43" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="P44" s="2" t="inlineStr">
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1638,11 +1638,6 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="F45" t="inlineStr">
         <is>
           <t>UA</t>
@@ -1651,6 +1646,11 @@
       <c r="J45" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -1670,14 +1670,14 @@
           <t>UA</t>
         </is>
       </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -1736,6 +1736,11 @@
           <t>Monday</t>
         </is>
       </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr">
         <is>
           <t>UA</t>
@@ -1744,11 +1749,6 @@
       <c r="J49" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="L50" s="2" t="inlineStr">
+      <c r="R50" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1790,6 +1790,11 @@
           <t>Wednesday</t>
         </is>
       </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr">
         <is>
           <t>UA</t>
@@ -1798,11 +1803,6 @@
       <c r="J51" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="N52" s="2" t="inlineStr">
+      <c r="P52" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1849,14 +1849,14 @@
           <t>UA</t>
         </is>
       </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -1925,14 +1925,14 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="J56" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -1952,14 +1952,14 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="J57" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -1979,14 +1979,14 @@
           <t>UA</t>
         </is>
       </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -2033,14 +2033,14 @@
           <t>Friday</t>
         </is>
       </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>BH UHB</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>BH SM</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>BH UHB</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
           <t>BH SM</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>BH UHB</t>
         </is>
@@ -2126,7 +2126,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -2168,7 +2168,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="O65" s="2" t="inlineStr">
+      <c r="N65" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -2360,11 +2360,6 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="F71" t="inlineStr">
         <is>
           <t>UA</t>
@@ -2393,6 +2388,11 @@
       <c r="O71" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -2427,6 +2427,11 @@
           <t>UA</t>
         </is>
       </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="M72" t="inlineStr">
         <is>
           <t>UA</t>
@@ -2440,11 +2445,6 @@
       <c r="O72" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="P72" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -2464,14 +2464,14 @@
           <t>UA</t>
         </is>
       </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -2617,11 +2617,6 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="F77" t="inlineStr">
         <is>
           <t>UA</t>
@@ -2650,6 +2645,11 @@
       <c r="N77" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="O78" s="2" t="inlineStr">
+      <c r="R78" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -2711,11 +2711,6 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="F79" t="inlineStr">
         <is>
           <t>UA</t>
@@ -2729,6 +2724,11 @@
       <c r="J79" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -2748,6 +2748,11 @@
           <t>Thursday</t>
         </is>
       </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr">
         <is>
           <t>UA</t>
@@ -2766,11 +2771,6 @@
       <c r="M80" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="P80" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -2790,6 +2790,11 @@
           <t>UA</t>
         </is>
       </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
           <t>UA</t>
@@ -2808,11 +2813,6 @@
       <c r="P81" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="Q81" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="L86" s="2" t="inlineStr">
+      <c r="M86" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -2967,7 +2967,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="Q87" s="2" t="inlineStr">
+      <c r="P87" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -2999,7 +2999,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="P88" s="2" t="inlineStr">
+      <c r="Q88" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -3087,14 +3087,14 @@
           <t>Tuesday</t>
         </is>
       </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="J92" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -3131,14 +3131,14 @@
           <t>Thursday</t>
         </is>
       </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="J94" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="R94" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -3153,14 +3153,14 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="J95" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -3219,14 +3219,14 @@
           <t>Monday</t>
         </is>
       </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="J98" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="K98" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -3246,14 +3246,14 @@
           <t>Tuesday</t>
         </is>
       </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="J99" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="I100" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -3295,7 +3295,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="M101" s="2" t="inlineStr">
+      <c r="L101" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -3312,7 +3312,7 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="I102" s="2" t="inlineStr">
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -3378,14 +3378,14 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="J105" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -3400,14 +3400,14 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="J106" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -3422,7 +3422,7 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="I107" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -3449,7 +3449,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="Q108" s="2" t="inlineStr">
+      <c r="M108" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -3476,6 +3476,11 @@
           <t>UA</t>
         </is>
       </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="G109" t="inlineStr">
         <is>
           <t>UA</t>
@@ -3484,11 +3489,6 @@
       <c r="J109" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="K109" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -3552,12 +3552,12 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
+      <c r="H112" t="inlineStr">
         <is>
           <t>BH SM</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
+      <c r="K112" t="inlineStr">
         <is>
           <t>BH UHB</t>
         </is>
@@ -3584,11 +3584,6 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="J113" t="inlineStr">
         <is>
           <t>UA</t>
@@ -3602,6 +3597,11 @@
       <c r="P113" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="Q113" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -3626,6 +3626,11 @@
           <t>UA</t>
         </is>
       </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="G114" t="inlineStr">
         <is>
           <t>UA</t>
@@ -3634,11 +3639,6 @@
       <c r="J114" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="K114" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -3668,14 +3668,14 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="D115" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -3720,11 +3720,6 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="G116" t="inlineStr">
         <is>
           <t>UA</t>
@@ -3738,6 +3733,11 @@
       <c r="J116" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -3858,7 +3858,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="K120" s="2" t="inlineStr">
+      <c r="L120" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -3885,7 +3885,7 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -3922,11 +3922,6 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="I122" t="inlineStr">
         <is>
           <t>UA</t>
@@ -3940,6 +3935,11 @@
       <c r="N122" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="P122" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
@@ -3959,7 +3959,7 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -4035,11 +4035,6 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="I126" t="inlineStr">
         <is>
           <t>UA</t>
@@ -4048,6 +4043,11 @@
       <c r="J126" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
@@ -4067,14 +4067,14 @@
           <t>Tuesday</t>
         </is>
       </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="J127" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="N127" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
@@ -4094,14 +4094,14 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D128" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="J128" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
@@ -4121,14 +4121,14 @@
           <t>Thursday</t>
         </is>
       </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="J129" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="K129" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
@@ -4224,14 +4224,14 @@
           <t>Monday</t>
         </is>
       </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="J133" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="L133" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
@@ -4278,6 +4278,11 @@
           <t>Wednesday</t>
         </is>
       </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="J135" t="inlineStr">
         <is>
           <t>UA</t>
@@ -4286,11 +4291,6 @@
       <c r="Q135" t="inlineStr">
         <is>
           <t>OffRota</t>
-        </is>
-      </c>
-      <c r="R135" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -4305,11 +4305,6 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="I136" t="inlineStr">
         <is>
           <t>UA</t>
@@ -4323,6 +4318,11 @@
       <c r="Q136" t="inlineStr">
         <is>
           <t>OffRota</t>
+        </is>
+      </c>
+      <c r="R136" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -4342,11 +4342,6 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="I137" t="inlineStr">
         <is>
           <t>UA</t>
@@ -4355,6 +4350,11 @@
       <c r="J137" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
@@ -4482,7 +4482,7 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="K142" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -4568,14 +4568,14 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C145" s="3" t="inlineStr">
+      <c r="J145" s="4" t="inlineStr">
+        <is>
+          <t>WC UHB</t>
+        </is>
+      </c>
+      <c r="N145" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
-        </is>
-      </c>
-      <c r="J145" s="4" t="inlineStr">
-        <is>
-          <t>WC UHB</t>
         </is>
       </c>
     </row>
@@ -4590,14 +4590,14 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C146" s="3" t="inlineStr">
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t>WC UHB</t>
+        </is>
+      </c>
+      <c r="N146" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
-        </is>
-      </c>
-      <c r="J146" s="4" t="inlineStr">
-        <is>
-          <t>WC UHB</t>
         </is>
       </c>
     </row>
@@ -4617,7 +4617,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="J147" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -4644,7 +4644,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr">
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -4676,14 +4676,14 @@
           <t>UA</t>
         </is>
       </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="O149" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="P149" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
       <c r="Q149" t="inlineStr">
@@ -4703,14 +4703,14 @@
           <t>Thursday</t>
         </is>
       </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="D150" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="M150" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
@@ -4848,7 +4848,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -4880,7 +4880,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="K156" s="2" t="inlineStr">
+      <c r="P156" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -4907,7 +4907,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="L157" s="2" t="inlineStr">
+      <c r="M157" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -4929,6 +4929,11 @@
           <t>Friday</t>
         </is>
       </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="D158" t="inlineStr">
         <is>
           <t>UA</t>
@@ -4937,11 +4942,6 @@
       <c r="G158" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="N158" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
       <c r="Q158" t="inlineStr">
@@ -4961,7 +4961,7 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="H159" s="3" t="inlineStr">
+      <c r="C159" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
@@ -4983,7 +4983,7 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="H160" s="3" t="inlineStr">
+      <c r="C160" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
@@ -5010,7 +5010,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="I161" s="2" t="inlineStr">
+      <c r="J161" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -5037,6 +5037,11 @@
           <t>UA</t>
         </is>
       </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="N162" t="inlineStr">
         <is>
           <t>UA</t>
@@ -5045,11 +5050,6 @@
       <c r="Q162" t="inlineStr">
         <is>
           <t>OffRota</t>
-        </is>
-      </c>
-      <c r="R162" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -5074,14 +5074,14 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="O163" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="Q163" t="inlineStr">
         <is>
           <t>OffRota</t>
+        </is>
+      </c>
+      <c r="R163" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -5128,11 +5128,6 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="D165" t="inlineStr">
         <is>
           <t>UA</t>
@@ -5141,6 +5136,11 @@
       <c r="I165" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="Q165" t="inlineStr">
@@ -5160,14 +5160,14 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="M166" s="4" t="inlineStr">
+      <c r="H166" s="3" t="inlineStr">
+        <is>
+          <t>WC SM</t>
+        </is>
+      </c>
+      <c r="O166" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
-        </is>
-      </c>
-      <c r="N166" s="3" t="inlineStr">
-        <is>
-          <t>WC SM</t>
         </is>
       </c>
     </row>
@@ -5182,14 +5182,14 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="M167" s="4" t="inlineStr">
+      <c r="H167" s="3" t="inlineStr">
+        <is>
+          <t>WC SM</t>
+        </is>
+      </c>
+      <c r="O167" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
-        </is>
-      </c>
-      <c r="N167" s="3" t="inlineStr">
-        <is>
-          <t>WC SM</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="J168" s="2" t="inlineStr">
+      <c r="L168" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -5251,14 +5251,14 @@
           <t>UA</t>
         </is>
       </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="Q169" t="inlineStr">
         <is>
           <t>OffRota</t>
-        </is>
-      </c>
-      <c r="R169" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C170" s="2" t="inlineStr">
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -5300,14 +5300,14 @@
           <t>Thursday</t>
         </is>
       </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="I171" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="K171" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
       <c r="Q171" t="inlineStr">
@@ -5327,7 +5327,7 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="J172" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -5420,14 +5420,14 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="N176" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="Q176" t="inlineStr">
@@ -5447,14 +5447,14 @@
           <t>Wednesday</t>
         </is>
       </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="N177" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="P177" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
       <c r="Q177" t="inlineStr">
@@ -5474,11 +5474,6 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="H178" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="N178" t="inlineStr">
         <is>
           <t>UA</t>
@@ -5487,6 +5482,11 @@
       <c r="Q178" t="inlineStr">
         <is>
           <t>OffRota</t>
+        </is>
+      </c>
+      <c r="R178" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -5506,14 +5506,14 @@
           <t>UA</t>
         </is>
       </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="I179" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="J179" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
       <c r="Q179" t="inlineStr">
@@ -5533,14 +5533,14 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="L180" s="4" t="inlineStr">
+      <c r="F180" s="3" t="inlineStr">
+        <is>
+          <t>WC SM</t>
+        </is>
+      </c>
+      <c r="R180" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
-        </is>
-      </c>
-      <c r="O180" s="3" t="inlineStr">
-        <is>
-          <t>WC SM</t>
         </is>
       </c>
     </row>
@@ -5555,14 +5555,14 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="L181" s="4" t="inlineStr">
+      <c r="F181" s="3" t="inlineStr">
+        <is>
+          <t>WC SM</t>
+        </is>
+      </c>
+      <c r="R181" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
-        </is>
-      </c>
-      <c r="O181" s="3" t="inlineStr">
-        <is>
-          <t>WC SM</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>

--- a/on_call_rota_16people_colored.xlsx
+++ b/on_call_rota_16people_colored.xlsx
@@ -596,11 +596,6 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>UA</t>
@@ -609,6 +604,11 @@
       <c r="P4" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -694,14 +694,14 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -716,14 +716,14 @@
           <t>Wednesday</t>
         </is>
       </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -738,14 +738,14 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -831,6 +831,11 @@
           <t>Monday</t>
         </is>
       </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Academic</t>
@@ -844,11 +849,6 @@
       <c r="O14" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
           <t>Academic</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -900,11 +900,6 @@
           <t>Academic</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>UA</t>
@@ -913,6 +908,11 @@
       <c r="O16" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
           <t>Academic</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -964,7 +964,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1040,7 +1040,7 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1057,7 +1057,7 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1074,7 +1074,7 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1091,7 +1091,7 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1108,6 +1108,11 @@
           <t>Friday</t>
         </is>
       </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>UA</t>
@@ -1116,11 +1121,6 @@
       <c r="M25" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1201,7 +1201,7 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1223,7 +1223,7 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1245,6 +1245,11 @@
           <t>Thursday</t>
         </is>
       </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>UA</t>
@@ -1253,11 +1258,6 @@
       <c r="P31" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1343,14 +1343,14 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -1375,14 +1375,14 @@
           <t>Tuesday</t>
         </is>
       </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -1429,7 +1429,7 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1471,14 +1471,14 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -1584,11 +1584,6 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>UA</t>
@@ -1597,6 +1592,11 @@
       <c r="J43" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -1611,6 +1611,11 @@
           <t>Wednesday</t>
         </is>
       </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr">
         <is>
           <t>UA</t>
@@ -1619,11 +1624,6 @@
       <c r="J44" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1648,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="Q45" s="2" t="inlineStr">
+      <c r="P45" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1670,14 +1670,14 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="J46" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -1736,19 +1736,14 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="F49" t="inlineStr">
         <is>
           <t>UA</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>UA</t>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -1763,19 +1758,14 @@
           <t>Tuesday</t>
         </is>
       </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>UA</t>
-        </is>
-      </c>
-      <c r="R50" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -1790,19 +1780,14 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="F51" t="inlineStr">
         <is>
           <t>UA</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>UA</t>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -1817,19 +1802,14 @@
           <t>Thursday</t>
         </is>
       </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>UA</t>
-        </is>
-      </c>
-      <c r="P52" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -1849,14 +1829,9 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>UA</t>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1846,7 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
+      <c r="G54" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
@@ -1893,7 +1868,7 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr">
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
@@ -1925,12 +1900,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>UA</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
+      <c r="R56" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -1952,11 +1922,6 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>UA</t>
-        </is>
-      </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
@@ -1979,14 +1944,9 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>UA</t>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -2001,19 +1961,14 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="F59" t="inlineStr">
         <is>
           <t>UA</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>UA</t>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -2033,14 +1988,14 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>BH SM</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
         <is>
           <t>BH UHB</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>BH SM</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2059,7 @@
           <t>BH SM</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>BH UHB</t>
         </is>
@@ -2131,11 +2086,6 @@
           <t>On Call</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>UA</t>
-        </is>
-      </c>
       <c r="M64" t="inlineStr">
         <is>
           <t>UA</t>
@@ -2158,11 +2108,6 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>UA</t>
-        </is>
-      </c>
       <c r="M65" t="inlineStr">
         <is>
           <t>UA</t>
@@ -2195,11 +2140,6 @@
           <t>On Call</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>UA</t>
-        </is>
-      </c>
       <c r="M66" t="inlineStr">
         <is>
           <t>UA</t>
@@ -2217,6 +2157,11 @@
           <t>Friday</t>
         </is>
       </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr">
         <is>
           <t>UA</t>
@@ -2230,11 +2175,6 @@
       <c r="J67" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -2259,7 +2199,7 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="G68" s="3" t="inlineStr">
+      <c r="H68" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
@@ -2281,7 +2221,7 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="G69" s="3" t="inlineStr">
+      <c r="H69" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
@@ -2375,6 +2315,11 @@
           <t>UA</t>
         </is>
       </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="M71" t="inlineStr">
         <is>
           <t>UA</t>
@@ -2388,11 +2333,6 @@
       <c r="O71" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="Q71" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -2407,6 +2347,11 @@
           <t>Wednesday</t>
         </is>
       </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr">
         <is>
           <t>UA</t>
@@ -2425,11 +2370,6 @@
       <c r="J72" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -2464,11 +2404,6 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="F73" t="inlineStr">
         <is>
           <t>UA</t>
@@ -2502,6 +2437,11 @@
       <c r="P73" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2476,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="K74" s="2" t="inlineStr">
+      <c r="L74" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -2573,7 +2513,7 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="L75" s="4" t="inlineStr">
+      <c r="K75" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -2595,7 +2535,7 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="L76" s="4" t="inlineStr">
+      <c r="K76" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -2664,6 +2604,11 @@
           <t>Tuesday</t>
         </is>
       </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr">
         <is>
           <t>UA</t>
@@ -2692,11 +2637,6 @@
       <c r="N78" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="R78" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2666,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="K79" s="2" t="inlineStr">
+      <c r="L79" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -2748,11 +2688,6 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="F80" t="inlineStr">
         <is>
           <t>UA</t>
@@ -2771,6 +2706,11 @@
       <c r="M80" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -2790,11 +2730,6 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="I81" t="inlineStr">
         <is>
           <t>UA</t>
@@ -2813,6 +2748,11 @@
       <c r="P81" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2767,7 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="K82" s="4" t="inlineStr">
+      <c r="L82" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -2849,7 +2789,7 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="K83" s="4" t="inlineStr">
+      <c r="L83" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -2881,11 +2821,6 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>UA</t>
-        </is>
-      </c>
       <c r="M84" t="inlineStr">
         <is>
           <t>UA</t>
@@ -2913,11 +2848,6 @@
           <t>On Call</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>UA</t>
-        </is>
-      </c>
       <c r="N85" t="inlineStr">
         <is>
           <t>UA</t>
@@ -2935,11 +2865,6 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>UA</t>
-        </is>
-      </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
@@ -2962,12 +2887,7 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>UA</t>
-        </is>
-      </c>
-      <c r="P87" s="2" t="inlineStr">
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -2989,19 +2909,14 @@
           <t>UA</t>
         </is>
       </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>UA</t>
-        </is>
-      </c>
-      <c r="Q88" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -3026,7 +2941,7 @@
           <t>WC SM</t>
         </is>
       </c>
-      <c r="M89" s="4" t="inlineStr">
+      <c r="J89" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -3048,7 +2963,7 @@
           <t>WC SM</t>
         </is>
       </c>
-      <c r="M90" s="4" t="inlineStr">
+      <c r="J90" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -3065,12 +2980,12 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>BH SM</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t>BH UHB</t>
         </is>
@@ -3087,14 +3002,9 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>UA</t>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -3109,12 +3019,7 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>UA</t>
-        </is>
-      </c>
-      <c r="N93" s="2" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -3131,14 +3036,9 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>UA</t>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -3153,14 +3053,14 @@
           <t>Friday</t>
         </is>
       </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="J95" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="P95" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -3219,14 +3119,9 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>UA</t>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -3246,14 +3141,9 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>UA</t>
+      <c r="R99" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -3268,14 +3158,9 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>UA</t>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -3290,11 +3175,6 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>UA</t>
-        </is>
-      </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
@@ -3312,14 +3192,9 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>UA</t>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3214,7 @@
           <t>WC SM</t>
         </is>
       </c>
-      <c r="K103" s="4" t="inlineStr">
+      <c r="M103" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -3361,7 +3236,7 @@
           <t>WC SM</t>
         </is>
       </c>
-      <c r="K104" s="4" t="inlineStr">
+      <c r="M104" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -3378,12 +3253,7 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>UA</t>
-        </is>
-      </c>
-      <c r="K105" s="2" t="inlineStr">
+      <c r="I105" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -3400,11 +3270,6 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>UA</t>
-        </is>
-      </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
@@ -3422,14 +3287,9 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>UA</t>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -3444,11 +3304,6 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>UA</t>
-        </is>
-      </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
@@ -3476,19 +3331,14 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="G109" t="inlineStr">
         <is>
           <t>UA</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>UA</t>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -3513,7 +3363,7 @@
           <t>WC SM</t>
         </is>
       </c>
-      <c r="L110" s="4" t="inlineStr">
+      <c r="J110" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -3535,7 +3385,7 @@
           <t>WC SM</t>
         </is>
       </c>
-      <c r="L111" s="4" t="inlineStr">
+      <c r="J111" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -3552,12 +3402,12 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
+      <c r="C112" t="inlineStr">
         <is>
           <t>BH SM</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
+      <c r="I112" t="inlineStr">
         <is>
           <t>BH UHB</t>
         </is>
@@ -3579,16 +3429,16 @@
           <t>UA</t>
         </is>
       </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="G113" t="inlineStr">
         <is>
           <t>UA</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>UA</t>
-        </is>
-      </c>
       <c r="O113" t="inlineStr">
         <is>
           <t>UA</t>
@@ -3597,11 +3447,6 @@
       <c r="P113" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="Q113" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -3626,19 +3471,14 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="G114" t="inlineStr">
         <is>
           <t>UA</t>
         </is>
       </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>UA</t>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -3673,21 +3513,11 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="G115" t="inlineStr">
         <is>
           <t>UA</t>
         </is>
       </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>UA</t>
-        </is>
-      </c>
       <c r="O115" t="inlineStr">
         <is>
           <t>UA</t>
@@ -3696,6 +3526,11 @@
       <c r="P115" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="Q115" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -3730,12 +3565,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>UA</t>
-        </is>
-      </c>
-      <c r="M116" s="2" t="inlineStr">
+      <c r="K116" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -3772,7 +3602,7 @@
           <t>WC SM</t>
         </is>
       </c>
-      <c r="Q117" s="4" t="inlineStr">
+      <c r="K117" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -3794,7 +3624,7 @@
           <t>WC SM</t>
         </is>
       </c>
-      <c r="Q118" s="4" t="inlineStr">
+      <c r="K118" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -3811,6 +3641,11 @@
           <t>Monday</t>
         </is>
       </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="G119" t="inlineStr">
         <is>
           <t>UA</t>
@@ -3821,19 +3656,9 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>UA</t>
-        </is>
-      </c>
       <c r="Q119" t="inlineStr">
         <is>
           <t>OffRota</t>
-        </is>
-      </c>
-      <c r="R119" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -3848,19 +3673,14 @@
           <t>Tuesday</t>
         </is>
       </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="I120" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>UA</t>
-        </is>
-      </c>
-      <c r="L120" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -3885,24 +3705,19 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D121" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="I121" t="inlineStr">
         <is>
           <t>UA</t>
         </is>
       </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>UA</t>
-        </is>
-      </c>
       <c r="N121" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="P121" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
@@ -3927,24 +3742,19 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>UA</t>
-        </is>
-      </c>
       <c r="N122" t="inlineStr">
         <is>
           <t>UA</t>
         </is>
       </c>
-      <c r="P122" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="Q122" t="inlineStr">
         <is>
           <t>OffRota</t>
+        </is>
+      </c>
+      <c r="R122" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -3959,17 +3769,12 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
-        <is>
-          <t>UA</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
         <is>
           <t>UA</t>
         </is>
@@ -4040,11 +3845,6 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>UA</t>
-        </is>
-      </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
@@ -4067,14 +3867,9 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="I127" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>UA</t>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
@@ -4094,12 +3889,7 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>UA</t>
-        </is>
-      </c>
-      <c r="N128" s="2" t="inlineStr">
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -4121,14 +3911,9 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>UA</t>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
@@ -4153,11 +3938,6 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>UA</t>
-        </is>
-      </c>
       <c r="Q130" t="inlineStr">
         <is>
           <t>OffRota</t>
@@ -4224,14 +4004,9 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="H133" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>UA</t>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
@@ -4251,12 +4026,7 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>UA</t>
-        </is>
-      </c>
-      <c r="O134" s="2" t="inlineStr">
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -4278,14 +4048,9 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>UA</t>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
@@ -4305,24 +4070,19 @@
           <t>Thursday</t>
         </is>
       </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="I136" t="inlineStr">
         <is>
           <t>UA</t>
         </is>
       </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>UA</t>
-        </is>
-      </c>
       <c r="Q136" t="inlineStr">
         <is>
           <t>OffRota</t>
-        </is>
-      </c>
-      <c r="R136" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -4342,19 +4102,14 @@
           <t>UA</t>
         </is>
       </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="I137" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>UA</t>
-        </is>
-      </c>
-      <c r="K137" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
@@ -4384,7 +4139,7 @@
           <t>WC SM</t>
         </is>
       </c>
-      <c r="K138" s="4" t="inlineStr">
+      <c r="J138" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -4406,7 +4161,7 @@
           <t>WC SM</t>
         </is>
       </c>
-      <c r="K139" s="4" t="inlineStr">
+      <c r="J139" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -4455,7 +4210,7 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="L141" s="2" t="inlineStr">
+      <c r="O141" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -4509,7 +4264,7 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="N143" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -4541,7 +4296,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="I144" s="2" t="inlineStr">
+      <c r="L144" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -4568,14 +4323,14 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="J145" s="4" t="inlineStr">
+      <c r="H145" s="3" t="inlineStr">
+        <is>
+          <t>WC SM</t>
+        </is>
+      </c>
+      <c r="L145" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
-        </is>
-      </c>
-      <c r="N145" s="3" t="inlineStr">
-        <is>
-          <t>WC SM</t>
         </is>
       </c>
     </row>
@@ -4590,14 +4345,14 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="J146" s="4" t="inlineStr">
+      <c r="H146" s="3" t="inlineStr">
+        <is>
+          <t>WC SM</t>
+        </is>
+      </c>
+      <c r="L146" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
-        </is>
-      </c>
-      <c r="N146" s="3" t="inlineStr">
-        <is>
-          <t>WC SM</t>
         </is>
       </c>
     </row>
@@ -4617,14 +4372,14 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="J147" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="Q147" t="inlineStr">
         <is>
           <t>OffRota</t>
+        </is>
+      </c>
+      <c r="R147" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -4644,7 +4399,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="N148" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -4676,7 +4431,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="I149" s="2" t="inlineStr">
+      <c r="L149" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -4703,14 +4458,14 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="D150" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
@@ -4745,7 +4500,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="L151" s="2" t="inlineStr">
+      <c r="I151" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -4816,14 +4571,14 @@
           <t>Monday</t>
         </is>
       </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="D154" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="J154" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
       <c r="Q154" t="inlineStr">
@@ -4880,7 +4635,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="P156" s="2" t="inlineStr">
+      <c r="I156" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -4907,7 +4662,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="M157" s="2" t="inlineStr">
+      <c r="J157" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -4929,11 +4684,6 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="D158" t="inlineStr">
         <is>
           <t>UA</t>
@@ -4942,6 +4692,11 @@
       <c r="G158" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="Q158" t="inlineStr">
@@ -4961,14 +4716,14 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C159" s="3" t="inlineStr">
+      <c r="K159" s="4" t="inlineStr">
+        <is>
+          <t>WC UHB</t>
+        </is>
+      </c>
+      <c r="N159" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
-        </is>
-      </c>
-      <c r="J159" s="4" t="inlineStr">
-        <is>
-          <t>WC UHB</t>
         </is>
       </c>
     </row>
@@ -4983,14 +4738,14 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C160" s="3" t="inlineStr">
+      <c r="K160" s="4" t="inlineStr">
+        <is>
+          <t>WC UHB</t>
+        </is>
+      </c>
+      <c r="N160" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
-        </is>
-      </c>
-      <c r="J160" s="4" t="inlineStr">
-        <is>
-          <t>WC UHB</t>
         </is>
       </c>
     </row>
@@ -5010,7 +4765,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="J161" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -5037,11 +4792,6 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="N162" t="inlineStr">
         <is>
           <t>UA</t>
@@ -5050,6 +4800,11 @@
       <c r="Q162" t="inlineStr">
         <is>
           <t>OffRota</t>
+        </is>
+      </c>
+      <c r="R162" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -5074,14 +4829,14 @@
           <t>UA</t>
         </is>
       </c>
+      <c r="P163" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="Q163" t="inlineStr">
         <is>
           <t>OffRota</t>
-        </is>
-      </c>
-      <c r="R163" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -5101,14 +4856,14 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="I164" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">
@@ -5160,12 +4915,12 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="H166" s="3" t="inlineStr">
+      <c r="C166" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
       </c>
-      <c r="O166" s="4" t="inlineStr">
+      <c r="M166" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -5182,12 +4937,12 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="H167" s="3" t="inlineStr">
+      <c r="C167" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
         </is>
       </c>
-      <c r="O167" s="4" t="inlineStr">
+      <c r="M167" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -5214,7 +4969,7 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="L168" s="2" t="inlineStr">
+      <c r="K168" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -5246,14 +5001,14 @@
           <t>UA</t>
         </is>
       </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="I169" t="inlineStr">
         <is>
           <t>UA</t>
-        </is>
-      </c>
-      <c r="K169" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
       <c r="Q169" t="inlineStr">
@@ -5300,14 +5055,14 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="I171" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="Q171" t="inlineStr">
@@ -5327,7 +5082,7 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="J172" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -5354,7 +5109,7 @@
           <t>WC SM</t>
         </is>
       </c>
-      <c r="J173" s="4" t="inlineStr">
+      <c r="I173" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -5376,7 +5131,7 @@
           <t>WC SM</t>
         </is>
       </c>
-      <c r="J174" s="4" t="inlineStr">
+      <c r="I174" s="4" t="inlineStr">
         <is>
           <t>WC UHB</t>
         </is>
@@ -5447,7 +5202,7 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="J177" s="2" t="inlineStr">
+      <c r="C177" s="2" t="inlineStr">
         <is>
           <t>On Call</t>
         </is>
@@ -5474,6 +5229,11 @@
           <t>Thursday</t>
         </is>
       </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
       <c r="N178" t="inlineStr">
         <is>
           <t>UA</t>
@@ -5482,11 +5242,6 @@
       <c r="Q178" t="inlineStr">
         <is>
           <t>OffRota</t>
-        </is>
-      </c>
-      <c r="R178" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
         </is>
       </c>
     </row>
@@ -5506,14 +5261,14 @@
           <t>UA</t>
         </is>
       </c>
-      <c r="H179" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="I179" t="inlineStr">
         <is>
           <t>UA</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
       <c r="Q179" t="inlineStr">
@@ -5533,14 +5288,14 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="F180" s="3" t="inlineStr">
+      <c r="K180" s="4" t="inlineStr">
+        <is>
+          <t>WC UHB</t>
+        </is>
+      </c>
+      <c r="O180" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
-        </is>
-      </c>
-      <c r="R180" s="4" t="inlineStr">
-        <is>
-          <t>WC UHB</t>
         </is>
       </c>
     </row>
@@ -5555,14 +5310,14 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="F181" s="3" t="inlineStr">
+      <c r="K181" s="4" t="inlineStr">
+        <is>
+          <t>WC UHB</t>
+        </is>
+      </c>
+      <c r="O181" s="3" t="inlineStr">
         <is>
           <t>WC SM</t>
-        </is>
-      </c>
-      <c r="R181" s="4" t="inlineStr">
-        <is>
-          <t>WC UHB</t>
         </is>
       </c>
     </row>
@@ -5604,11 +5359,6 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
-        <is>
-          <t>On Call</t>
-        </is>
-      </c>
       <c r="I183" t="inlineStr">
         <is>
           <t>UA</t>
@@ -5617,6 +5367,11 @@
       <c r="Q183" t="inlineStr">
         <is>
           <t>OffRota</t>
+        </is>
+      </c>
+      <c r="R183" s="2" t="inlineStr">
+        <is>
+          <t>On Call</t>
         </is>
       </c>
     </row>
